--- a/agriculture 55.xlsx
+++ b/agriculture 55.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate of APY Statisticts of Arecanut in India(1964-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -216,7 +213,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -238,14 +235,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -326,24 +315,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -380,36 +365,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -417,781 +399,777 @@
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="6" t="n">
+        <v>4.58015267175573</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5.30973451327434</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.695249130938591</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>4.58015267175573</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>5.30973451327434</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0.695249130938591</v>
+      <c r="B5" s="6" t="n">
+        <v>3.64963503649636</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>9.24369747899159</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5.29344073647871</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>3.64963503649636</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>9.24369747899159</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>5.29344073647871</v>
+      <c r="B6" s="6" t="n">
+        <v>3.52112676056338</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3.84615384615385</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.327868852459012</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>3.52112676056338</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>3.84615384615385</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>0.327868852459012</v>
+      <c r="B7" s="6" t="n">
+        <v>6.80272108843538</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3.7037037037037</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-2.8322440087146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>6.80272108843538</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>3.7037037037037</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>-2.8322440087146</v>
+      <c r="B8" s="6" t="n">
+        <v>2.54777070063694</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-1.42857142857142</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-3.92376681614349</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>2.54777070063694</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>-1.42857142857142</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>-3.92376681614349</v>
+      <c r="B9" s="6" t="n">
+        <v>3.72670807453417</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2.17391304347827</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1.51691948658109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>3.72670807453417</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2.17391304347827</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>-1.51691948658109</v>
+      <c r="B10" s="6" t="n">
+        <v>4.19161676646707</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4.32624113475177</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.118483412322279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>4.19161676646707</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>4.32624113475177</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0.118483412322279</v>
+      <c r="B11" s="6" t="n">
+        <v>2.29885057471264</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.611828687967364</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-1.65680473372781</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>2.29885057471264</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>0.611828687967364</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>-1.65680473372781</v>
+      <c r="B12" s="6" t="n">
+        <v>3.93258426966292</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12.8378378378378</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>8.66425992779782</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="7" t="n">
-        <v>3.93258426966292</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>12.8378378378378</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>8.66425992779782</v>
+      <c r="B13" s="6" t="n">
+        <v>2.16216216216216</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-1.19760479041916</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-3.32225913621262</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>2.16216216216216</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>-1.19760479041916</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>-3.32225913621262</v>
+      <c r="B14" s="6" t="n">
+        <v>-5.82010582010583</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-3.03030303030303</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2.97823596792668</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>-5.82010582010583</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>-3.03030303030303</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>2.97823596792668</v>
+      <c r="B15" s="6" t="n">
+        <v>-3.93258426966292</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7.34149054505007</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>-3.93258426966292</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>7.34149054505007</v>
+      <c r="B16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>6.06060606060606</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>6.01036269430051</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="6" t="n">
+        <v>4.67836257309942</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-0.586510263929618</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2.23463687150838</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4.3956043956044</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2.06489675516224</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1.09289617486339</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>3.15789473684211</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.92678227360308</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-1.08108108108108</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-1.02040816326531</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.189035916824198</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0.546448087431695</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>4.12371134020619</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.58490566037737</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1.08695652173914</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-5.94059405940595</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-6.92167577413479</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>6.06060606060606</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>6.01036269430051</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>4.67836257309942</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-0.586510263929618</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>2.23463687150838</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>4.3956043956044</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>2.06489675516224</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>1.09289617486339</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>3.15789473684211</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1.92678227360308</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>-1.08108108108108</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>-1.02040816326531</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>0.189035916824198</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>0.546448087431695</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>4.12371134020619</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>3.58490566037737</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>1.08695652173914</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>-5.94059405940595</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>-6.92167577413479</v>
+      <c r="C23" s="6" t="n">
+        <v>15.2631578947368</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>15.1663405088063</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>15.2631578947368</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>15.1663405088063</v>
+      <c r="C24" s="6" t="n">
+        <v>-1.36986301369864</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>-1.35938827527613</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>-1.36986301369864</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>-1.35938827527613</v>
+      <c r="B25" s="6" t="n">
+        <v>4.83870967741935</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1.38888888888888</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-3.18690783807063</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>4.83870967741935</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>1.38888888888888</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>-3.18690783807063</v>
+      <c r="B26" s="6" t="n">
+        <v>2.56410256410255</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>3.65296803652968</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.978647686832734</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>2.56410256410255</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>3.65296803652968</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0.978647686832734</v>
+      <c r="B27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>9.69162995594715</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>7.57709251101322</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>9.69162995594715</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>7.57709251101322</v>
+      <c r="B28" s="6" t="n">
+        <v>2.94117647058822</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.803212851405632</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-1.71990171990172</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="n">
-        <v>2.94117647058822</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>0.803212851405632</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>-1.71990171990172</v>
+      <c r="B29" s="6" t="n">
+        <v>3.33333333333334</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-4.7808764940239</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-8.41666666666666</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>3.33333333333334</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>-4.7808764940239</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>-8.41666666666666</v>
+      <c r="B30" s="6" t="n">
+        <v>2.30414746543779</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>5.02092050209204</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>3.00272975432212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>2.30414746543779</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>5.02092050209204</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>3.00272975432212</v>
+      <c r="B31" s="6" t="n">
+        <v>2.25225225225225</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1.99203187250996</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.0883392226148416</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>2.25225225225225</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>1.99203187250996</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>-0.0883392226148416</v>
+      <c r="B32" s="6" t="n">
+        <v>3.96475770925111</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>5.859375</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1.76834659593281</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="7" t="n">
-        <v>3.96475770925111</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>5.859375</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>1.76834659593281</v>
+      <c r="B33" s="6" t="n">
+        <v>3.38983050847457</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>7.0110701107011</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.21459600347525</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>3.38983050847457</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>7.0110701107011</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>3.21459600347525</v>
+      <c r="B34" s="6" t="n">
+        <v>4.50819672131149</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1.89655172413794</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-2.44107744107744</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>4.50819672131149</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>1.89655172413794</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>-2.44107744107744</v>
+      <c r="B35" s="6" t="n">
+        <v>2.43137254901959</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>4.12859560067682</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>1.64106988783435</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>2.43137254901959</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>4.12859560067682</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1.64106988783435</v>
+      <c r="B36" s="6" t="n">
+        <v>4.78560490045943</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>8.38479038024049</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>3.43542554455782</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>4.78560490045943</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>8.38479038024049</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>3.43542554455782</v>
+      <c r="B37" s="6" t="n">
+        <v>1.38838143953235</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>-7.10644677661169</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>-8.37840277720785</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="7" t="n">
-        <v>1.38838143953235</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>-7.10644677661169</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>-8.37840277720785</v>
+      <c r="B38" s="6" t="n">
+        <v>4.14414414414415</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>7.94060684312459</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>3.64475098530992</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>4.14414414414415</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>7.94060684312459</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>3.64475098530992</v>
+      <c r="B39" s="6" t="n">
+        <v>9.06574394463668</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>11.5729665071771</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2.29887044223009</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>9.06574394463668</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>11.5729665071771</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>2.29887044223009</v>
+      <c r="B40" s="6" t="n">
+        <v>8.15355329949239</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>8.04073974805681</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>-0.103912341913848</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>8.15355329949239</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>8.04073974805681</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>-0.103912341913848</v>
+      <c r="B41" s="6" t="n">
+        <v>3.93077148723966</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>3.17539072190522</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>-0.727297329296561</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7" t="n">
-        <v>3.93077148723966</v>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>3.17539072190522</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>-0.727297329296561</v>
+      <c r="B42" s="6" t="n">
+        <v>3.02003951453571</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>5.6023082471748</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>2.50711328437805</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="7" t="n">
-        <v>3.02003951453571</v>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>5.6023082471748</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>2.50711328437805</v>
+      <c r="B43" s="6" t="n">
+        <v>-0.191780821917809</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>3.07377049180328</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>3.27186297567503</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="7" t="n">
-        <v>-0.191780821917809</v>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>3.07377049180328</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>3.27186297567503</v>
+      <c r="B44" s="6" t="n">
+        <v>4.6115838594565</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>6.71526397172522</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>2.01100864275023</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="7" t="n">
-        <v>4.6115838594565</v>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>6.71526397172522</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>2.01100864275023</v>
+      <c r="B45" s="6" t="n">
+        <v>0.335869850432946</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>-2.04305526806045</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>-2.37131700390487</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>0.335869850432946</v>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>-2.04305526806045</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>-2.37131700390487</v>
+      <c r="B46" s="6" t="n">
+        <v>1.12715100162142</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1.0227584895294</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>-0.103426821483688</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="7" t="n">
-        <v>1.12715100162142</v>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>1.0227584895294</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>-0.103426821483688</v>
+      <c r="B47" s="6" t="n">
+        <v>0.106028084512144</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>0.675633275461762</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0.569436468199713</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="7" t="n">
-        <v>0.106028084512144</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>0.675633275461762</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0.569436468199713</v>
+      <c r="B48" s="6" t="n">
+        <v>3.35830534745545</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>-0.685643050072726</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>-3.9128161820887</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="7" t="n">
-        <v>3.35830534745545</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>-0.685643050072726</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>-3.9128161820887</v>
+      <c r="B49" s="6" t="n">
+        <v>0.0499875031242159</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>0.0209205020920589</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>-0.029296057587691</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="7" t="n">
-        <v>0.0499875031242159</v>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>0.0209205020920589</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>-0.029296057587691</v>
+      <c r="B50" s="6" t="n">
+        <v>15.8880839370472</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>42.3760719514746</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>22.8567840247833</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="7" t="n">
-        <v>15.8880839370472</v>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>42.3760719514746</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>22.8567840247833</v>
+      <c r="B51" s="6" t="n">
+        <v>-3.77236473377883</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>-10.5773468488321</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>-7.07129908541988</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="7" t="n">
-        <v>-3.77236473377883</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>-10.5773468488321</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>-7.07129908541988</v>
+      <c r="B52" s="6" t="n">
+        <v>1.23207885304659</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2.22934121899128</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0.984907376171562</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>1.23207885304659</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>2.22934121899128</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>0.984907376171562</v>
+      <c r="B53" s="6" t="n">
+        <v>-0.420447001549007</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>20.0443537371238</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>20.5510490119897</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="7" t="n">
-        <v>-0.420447001549007</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>20.0443537371238</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>20.5510490119897</v>
+      <c r="B54" s="6" t="n">
+        <v>5.33333333333332</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>-4.41767068273092</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>-9.25722891566265</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="7" t="n">
-        <v>5.33333333333332</v>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>-4.41767068273092</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>-9.25722891566265</v>
+      <c r="B55" s="6" t="n">
+        <v>-4.0084388185654</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>1.26050420168067</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>5.48883710740675</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>-4.0084388185654</v>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>1.26050420168067</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>5.48883710740675</v>
+      <c r="B56" s="6" t="n">
+        <v>9.23076923076922</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>15.2143845089903</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>5.47825375548296</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="7" t="n">
-        <v>9.23076923076922</v>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>15.2143845089903</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>5.47825375548296</v>
+      <c r="B57" s="6" t="n">
+        <v>5.03018108651911</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>8.16326530612246</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>2.982590122072</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>5.03018108651911</v>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>8.16326530612246</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>2.982590122072</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" s="7" t="n">
+      <c r="B58" s="6" t="n">
         <v>-1.91570881226054</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C58" s="6" t="n">
         <v>-8.10210876803552</v>
       </c>
-      <c r="D59" s="7" t="n">
+      <c r="D58" s="6" t="n">
         <v>-6.30688566379884</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 55.xlsx
+++ b/agriculture 55.xlsx
@@ -202,7 +202,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
 </sst>
 </file>
@@ -213,7 +213,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -235,13 +235,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -324,7 +317,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -344,7 +337,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/agriculture 55.xlsx
+++ b/agriculture 55.xlsx
@@ -202,7 +202,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
 </sst>
 </file>
